--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH846"/>
+  <dimension ref="A1:AH847"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65787,6 +65787,68 @@
       </c>
       <c r="AH846" t="inlineStr"/>
     </row>
+    <row r="847">
+      <c r="A847" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B847" t="n">
+        <v>0.5757265385</v>
+      </c>
+      <c r="C847" t="n">
+        <v>0.09181755549999999</v>
+      </c>
+      <c r="D847" t="inlineStr"/>
+      <c r="E847" t="inlineStr"/>
+      <c r="F847" t="inlineStr"/>
+      <c r="G847" t="inlineStr"/>
+      <c r="H847" t="inlineStr"/>
+      <c r="I847" t="n">
+        <v>0.045089856</v>
+      </c>
+      <c r="J847" t="inlineStr"/>
+      <c r="K847" t="n">
+        <v>1585.244142588777</v>
+      </c>
+      <c r="L847" t="inlineStr"/>
+      <c r="M847" t="inlineStr"/>
+      <c r="N847" t="inlineStr"/>
+      <c r="O847" t="n">
+        <v>0.008803838999999999</v>
+      </c>
+      <c r="P847" t="inlineStr"/>
+      <c r="Q847" t="n">
+        <v>8.207999999999999e-07</v>
+      </c>
+      <c r="R847" t="inlineStr"/>
+      <c r="S847" t="inlineStr"/>
+      <c r="T847" t="inlineStr"/>
+      <c r="U847" t="inlineStr"/>
+      <c r="V847" t="inlineStr"/>
+      <c r="W847" t="inlineStr"/>
+      <c r="X847" t="inlineStr"/>
+      <c r="Y847" t="inlineStr"/>
+      <c r="Z847" t="inlineStr"/>
+      <c r="AA847" t="n">
+        <v>0.8383524127552</v>
+      </c>
+      <c r="AB847" t="n">
+        <v>165.0376824185</v>
+      </c>
+      <c r="AC847" t="n">
+        <v>7.881425888176801</v>
+      </c>
+      <c r="AD847" t="n">
+        <v>0.10315916</v>
+      </c>
+      <c r="AE847" t="n">
+        <v>1759.847545637009</v>
+      </c>
+      <c r="AF847" t="inlineStr"/>
+      <c r="AG847" t="n">
+        <v>0.021344559</v>
+      </c>
+      <c r="AH847" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH847"/>
+  <dimension ref="A1:AH849"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65849,6 +65849,130 @@
       </c>
       <c r="AH847" t="inlineStr"/>
     </row>
+    <row r="848">
+      <c r="A848" s="2" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B848" t="n">
+        <v>0.5724729744999999</v>
+      </c>
+      <c r="C848" t="n">
+        <v>0.09004258500000001</v>
+      </c>
+      <c r="D848" t="inlineStr"/>
+      <c r="E848" t="inlineStr"/>
+      <c r="F848" t="inlineStr"/>
+      <c r="G848" t="inlineStr"/>
+      <c r="H848" t="inlineStr"/>
+      <c r="I848" t="n">
+        <v>0.04399983</v>
+      </c>
+      <c r="J848" t="inlineStr"/>
+      <c r="K848" t="n">
+        <v>1578.248360847432</v>
+      </c>
+      <c r="L848" t="inlineStr"/>
+      <c r="M848" t="inlineStr"/>
+      <c r="N848" t="inlineStr"/>
+      <c r="O848" t="n">
+        <v>0.008668561</v>
+      </c>
+      <c r="P848" t="inlineStr"/>
+      <c r="Q848" t="n">
+        <v>8.088e-07</v>
+      </c>
+      <c r="R848" t="inlineStr"/>
+      <c r="S848" t="inlineStr"/>
+      <c r="T848" t="inlineStr"/>
+      <c r="U848" t="inlineStr"/>
+      <c r="V848" t="inlineStr"/>
+      <c r="W848" t="inlineStr"/>
+      <c r="X848" t="inlineStr"/>
+      <c r="Y848" t="inlineStr"/>
+      <c r="Z848" t="inlineStr"/>
+      <c r="AA848" t="n">
+        <v>0.8385703756639999</v>
+      </c>
+      <c r="AB848" t="n">
+        <v>156.134003125</v>
+      </c>
+      <c r="AC848" t="n">
+        <v>7.6764715506592</v>
+      </c>
+      <c r="AD848" t="n">
+        <v>0.10060752</v>
+      </c>
+      <c r="AE848" t="n">
+        <v>1743.734578530055</v>
+      </c>
+      <c r="AF848" t="inlineStr"/>
+      <c r="AG848" t="n">
+        <v>0.021380352</v>
+      </c>
+      <c r="AH848" t="inlineStr"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B849" t="n">
+        <v>0.5825096145000001</v>
+      </c>
+      <c r="C849" t="n">
+        <v>0.09144751250000001</v>
+      </c>
+      <c r="D849" t="inlineStr"/>
+      <c r="E849" t="inlineStr"/>
+      <c r="F849" t="inlineStr"/>
+      <c r="G849" t="inlineStr"/>
+      <c r="H849" t="inlineStr"/>
+      <c r="I849" t="n">
+        <v>0.045431043</v>
+      </c>
+      <c r="J849" t="inlineStr"/>
+      <c r="K849" t="n">
+        <v>1576.849204499163</v>
+      </c>
+      <c r="L849" t="inlineStr"/>
+      <c r="M849" t="inlineStr"/>
+      <c r="N849" t="inlineStr"/>
+      <c r="O849" t="n">
+        <v>0.008717081999999999</v>
+      </c>
+      <c r="P849" t="inlineStr"/>
+      <c r="Q849" t="n">
+        <v>8.303999999999999e-07</v>
+      </c>
+      <c r="R849" t="inlineStr"/>
+      <c r="S849" t="inlineStr"/>
+      <c r="T849" t="inlineStr"/>
+      <c r="U849" t="inlineStr"/>
+      <c r="V849" t="inlineStr"/>
+      <c r="W849" t="inlineStr"/>
+      <c r="X849" t="inlineStr"/>
+      <c r="Y849" t="inlineStr"/>
+      <c r="Z849" t="inlineStr"/>
+      <c r="AA849" t="n">
+        <v>0.8383775623216</v>
+      </c>
+      <c r="AB849" t="n">
+        <v>170.99061274</v>
+      </c>
+      <c r="AC849" t="n">
+        <v>7.732368188164</v>
+      </c>
+      <c r="AD849" t="n">
+        <v>0.10179221</v>
+      </c>
+      <c r="AE849" t="n">
+        <v>1757.261599037048</v>
+      </c>
+      <c r="AF849" t="inlineStr"/>
+      <c r="AG849" t="n">
+        <v>0.021137755</v>
+      </c>
+      <c r="AH849" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH849"/>
+  <dimension ref="A1:AH852"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65973,6 +65973,192 @@
       </c>
       <c r="AH849" t="inlineStr"/>
     </row>
+    <row r="850">
+      <c r="A850" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B850" t="n">
+        <v>0.5635513759999999</v>
+      </c>
+      <c r="C850" t="n">
+        <v>0.08717675100000001</v>
+      </c>
+      <c r="D850" t="inlineStr"/>
+      <c r="E850" t="inlineStr"/>
+      <c r="F850" t="inlineStr"/>
+      <c r="G850" t="inlineStr"/>
+      <c r="H850" t="inlineStr"/>
+      <c r="I850" t="n">
+        <v>0.042927528</v>
+      </c>
+      <c r="J850" t="inlineStr"/>
+      <c r="K850" t="n">
+        <v>1552.597161129167</v>
+      </c>
+      <c r="L850" t="inlineStr"/>
+      <c r="M850" t="inlineStr"/>
+      <c r="N850" t="inlineStr"/>
+      <c r="O850" t="n">
+        <v>0.008615925999999999</v>
+      </c>
+      <c r="P850" t="inlineStr"/>
+      <c r="Q850" t="n">
+        <v>8.112e-07</v>
+      </c>
+      <c r="R850" t="inlineStr"/>
+      <c r="S850" t="inlineStr"/>
+      <c r="T850" t="inlineStr"/>
+      <c r="U850" t="inlineStr"/>
+      <c r="V850" t="inlineStr"/>
+      <c r="W850" t="inlineStr"/>
+      <c r="X850" t="inlineStr"/>
+      <c r="Y850" t="inlineStr"/>
+      <c r="Z850" t="inlineStr"/>
+      <c r="AA850" t="n">
+        <v>0.8388302545167999</v>
+      </c>
+      <c r="AB850" t="n">
+        <v>163.1772998495</v>
+      </c>
+      <c r="AC850" t="n">
+        <v>7.434252788138399</v>
+      </c>
+      <c r="AD850" t="n">
+        <v>0.09878492</v>
+      </c>
+      <c r="AE850" t="n">
+        <v>1724.868991412522</v>
+      </c>
+      <c r="AF850" t="inlineStr"/>
+      <c r="AG850" t="n">
+        <v>0.020390079</v>
+      </c>
+      <c r="AH850" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B851" t="n">
+        <v>0.5677347745</v>
+      </c>
+      <c r="C851" t="n">
+        <v>0.08790375100000002</v>
+      </c>
+      <c r="D851" t="inlineStr"/>
+      <c r="E851" t="inlineStr"/>
+      <c r="F851" t="inlineStr"/>
+      <c r="G851" t="inlineStr"/>
+      <c r="H851" t="inlineStr"/>
+      <c r="I851" t="n">
+        <v>0.04371624599999999</v>
+      </c>
+      <c r="J851" t="inlineStr"/>
+      <c r="K851" t="n">
+        <v>1565.189568263588</v>
+      </c>
+      <c r="L851" t="inlineStr"/>
+      <c r="M851" t="inlineStr"/>
+      <c r="N851" t="inlineStr"/>
+      <c r="O851" t="n">
+        <v>0.008783632</v>
+      </c>
+      <c r="P851" t="inlineStr"/>
+      <c r="Q851" t="n">
+        <v>8.184e-07</v>
+      </c>
+      <c r="R851" t="inlineStr"/>
+      <c r="S851" t="inlineStr"/>
+      <c r="T851" t="inlineStr"/>
+      <c r="U851" t="inlineStr"/>
+      <c r="V851" t="inlineStr"/>
+      <c r="W851" t="inlineStr"/>
+      <c r="X851" t="inlineStr"/>
+      <c r="Y851" t="inlineStr"/>
+      <c r="Z851" t="inlineStr"/>
+      <c r="AA851" t="n">
+        <v>0.8388637872720001</v>
+      </c>
+      <c r="AB851" t="n">
+        <v>196.6024672385</v>
+      </c>
+      <c r="AC851" t="n">
+        <v>7.359723938132</v>
+      </c>
+      <c r="AD851" t="n">
+        <v>0.10078978</v>
+      </c>
+      <c r="AE851" t="n">
+        <v>1770.820109342392</v>
+      </c>
+      <c r="AF851" t="inlineStr"/>
+      <c r="AG851" t="n">
+        <v>0.020557113</v>
+      </c>
+      <c r="AH851" t="inlineStr"/>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B852" t="n">
+        <v>0.5693067245</v>
+      </c>
+      <c r="C852" t="n">
+        <v>0.08895862800000001</v>
+      </c>
+      <c r="D852" t="inlineStr"/>
+      <c r="E852" t="inlineStr"/>
+      <c r="F852" t="inlineStr"/>
+      <c r="G852" t="inlineStr"/>
+      <c r="H852" t="inlineStr"/>
+      <c r="I852" t="n">
+        <v>0.045036684</v>
+      </c>
+      <c r="J852" t="inlineStr"/>
+      <c r="K852" t="n">
+        <v>1562.39125556705</v>
+      </c>
+      <c r="L852" t="inlineStr"/>
+      <c r="M852" t="inlineStr"/>
+      <c r="N852" t="inlineStr"/>
+      <c r="O852" t="n">
+        <v>0.008934156</v>
+      </c>
+      <c r="P852" t="inlineStr"/>
+      <c r="Q852" t="n">
+        <v>8.664e-07</v>
+      </c>
+      <c r="R852" t="inlineStr"/>
+      <c r="S852" t="inlineStr"/>
+      <c r="T852" t="inlineStr"/>
+      <c r="U852" t="inlineStr"/>
+      <c r="V852" t="inlineStr"/>
+      <c r="W852" t="inlineStr"/>
+      <c r="X852" t="inlineStr"/>
+      <c r="Y852" t="inlineStr"/>
+      <c r="Z852" t="inlineStr"/>
+      <c r="AA852" t="n">
+        <v>0.8389140864048</v>
+      </c>
+      <c r="AB852" t="n">
+        <v>215.551624606</v>
+      </c>
+      <c r="AC852" t="n">
+        <v>7.6019427006528</v>
+      </c>
+      <c r="AD852" t="n">
+        <v>0.106576535</v>
+      </c>
+      <c r="AE852" t="n">
+        <v>1787.224006469007</v>
+      </c>
+      <c r="AF852" t="inlineStr"/>
+      <c r="AG852" t="n">
+        <v>0.021455915</v>
+      </c>
+      <c r="AH852" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH852"/>
+  <dimension ref="A1:AH854"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66159,6 +66159,130 @@
       </c>
       <c r="AH852" t="inlineStr"/>
     </row>
+    <row r="853">
+      <c r="A853" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B853" t="n">
+        <v>0.6025848315</v>
+      </c>
+      <c r="C853" t="n">
+        <v>0.09495128900000001</v>
+      </c>
+      <c r="D853" t="inlineStr"/>
+      <c r="E853" t="inlineStr"/>
+      <c r="F853" t="inlineStr"/>
+      <c r="G853" t="inlineStr"/>
+      <c r="H853" t="inlineStr"/>
+      <c r="I853" t="n">
+        <v>0.049946232</v>
+      </c>
+      <c r="J853" t="inlineStr"/>
+      <c r="K853" t="n">
+        <v>1577.781975398009</v>
+      </c>
+      <c r="L853" t="inlineStr"/>
+      <c r="M853" t="inlineStr"/>
+      <c r="N853" t="inlineStr"/>
+      <c r="O853" t="n">
+        <v>0.009211850999999998</v>
+      </c>
+      <c r="P853" t="inlineStr"/>
+      <c r="Q853" t="n">
+        <v>9.168e-07</v>
+      </c>
+      <c r="R853" t="inlineStr"/>
+      <c r="S853" t="inlineStr"/>
+      <c r="T853" t="inlineStr"/>
+      <c r="U853" t="inlineStr"/>
+      <c r="V853" t="inlineStr"/>
+      <c r="W853" t="inlineStr"/>
+      <c r="X853" t="inlineStr"/>
+      <c r="Y853" t="inlineStr"/>
+      <c r="Z853" t="inlineStr"/>
+      <c r="AA853" t="n">
+        <v>0.8384278614544</v>
+      </c>
+      <c r="AB853" t="n">
+        <v>229.5456397755</v>
+      </c>
+      <c r="AC853" t="n">
+        <v>7.91869031318</v>
+      </c>
+      <c r="AD853" t="n">
+        <v>0.11637301</v>
+      </c>
+      <c r="AE853" t="n">
+        <v>1816.980927733443</v>
+      </c>
+      <c r="AF853" t="inlineStr"/>
+      <c r="AG853" t="n">
+        <v>0.023126255</v>
+      </c>
+      <c r="AH853" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B854" t="n">
+        <v>0.6053124255</v>
+      </c>
+      <c r="C854" t="n">
+        <v>0.09569828150000001</v>
+      </c>
+      <c r="D854" t="inlineStr"/>
+      <c r="E854" t="inlineStr"/>
+      <c r="F854" t="inlineStr"/>
+      <c r="G854" t="inlineStr"/>
+      <c r="H854" t="inlineStr"/>
+      <c r="I854" t="n">
+        <v>0.049210686</v>
+      </c>
+      <c r="J854" t="inlineStr"/>
+      <c r="K854" t="n">
+        <v>1585.244142588777</v>
+      </c>
+      <c r="L854" t="inlineStr"/>
+      <c r="M854" t="inlineStr"/>
+      <c r="N854" t="inlineStr"/>
+      <c r="O854" t="n">
+        <v>0.009220441999999999</v>
+      </c>
+      <c r="P854" t="inlineStr"/>
+      <c r="Q854" t="n">
+        <v>9.863999999999998e-07</v>
+      </c>
+      <c r="R854" t="inlineStr"/>
+      <c r="S854" t="inlineStr"/>
+      <c r="T854" t="inlineStr"/>
+      <c r="U854" t="inlineStr"/>
+      <c r="V854" t="inlineStr"/>
+      <c r="W854" t="inlineStr"/>
+      <c r="X854" t="inlineStr"/>
+      <c r="Y854" t="inlineStr"/>
+      <c r="Z854" t="inlineStr"/>
+      <c r="AA854" t="n">
+        <v>0.8384949269648</v>
+      </c>
+      <c r="AB854" t="n">
+        <v>216.157057164</v>
+      </c>
+      <c r="AC854" t="n">
+        <v>8.123644650697599</v>
+      </c>
+      <c r="AD854" t="n">
+        <v>0.116145185</v>
+      </c>
+      <c r="AE854" t="n">
+        <v>1811.262105292839</v>
+      </c>
+      <c r="AF854" t="inlineStr"/>
+      <c r="AG854" t="n">
+        <v>0.023177956</v>
+      </c>
+      <c r="AH854" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH854"/>
+  <dimension ref="A1:AH856"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66283,6 +66283,130 @@
       </c>
       <c r="AH854" t="inlineStr"/>
     </row>
+    <row r="855">
+      <c r="A855" s="2" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B855" t="n">
+        <v>0.6047761</v>
+      </c>
+      <c r="C855" t="n">
+        <v>0.09615338350000001</v>
+      </c>
+      <c r="D855" t="inlineStr"/>
+      <c r="E855" t="inlineStr"/>
+      <c r="F855" t="inlineStr"/>
+      <c r="G855" t="inlineStr"/>
+      <c r="H855" t="inlineStr"/>
+      <c r="I855" t="n">
+        <v>0.049259427</v>
+      </c>
+      <c r="J855" t="inlineStr"/>
+      <c r="K855" t="n">
+        <v>1598.302935172621</v>
+      </c>
+      <c r="L855" t="inlineStr"/>
+      <c r="M855" t="inlineStr"/>
+      <c r="N855" t="inlineStr"/>
+      <c r="O855" t="n">
+        <v>0.009347975999999999</v>
+      </c>
+      <c r="P855" t="inlineStr"/>
+      <c r="Q855" t="n">
+        <v>9.599999999999999e-07</v>
+      </c>
+      <c r="R855" t="inlineStr"/>
+      <c r="S855" t="inlineStr"/>
+      <c r="T855" t="inlineStr"/>
+      <c r="U855" t="inlineStr"/>
+      <c r="V855" t="inlineStr"/>
+      <c r="W855" t="inlineStr"/>
+      <c r="X855" t="inlineStr"/>
+      <c r="Y855" t="inlineStr"/>
+      <c r="Z855" t="inlineStr"/>
+      <c r="AA855" t="n">
+        <v>0.838444627832</v>
+      </c>
+      <c r="AB855" t="n">
+        <v>221.7661253045</v>
+      </c>
+      <c r="AC855" t="n">
+        <v>8.123644650697599</v>
+      </c>
+      <c r="AD855" t="n">
+        <v>0.11518832</v>
+      </c>
+      <c r="AE855" t="n">
+        <v>1829.92923682015</v>
+      </c>
+      <c r="AF855" t="inlineStr"/>
+      <c r="AG855" t="n">
+        <v>0.023360898</v>
+      </c>
+      <c r="AH855" t="inlineStr"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B856" t="n">
+        <v>0.645319</v>
+      </c>
+      <c r="C856" t="n">
+        <v>0.1009145065</v>
+      </c>
+      <c r="D856" t="inlineStr"/>
+      <c r="E856" t="inlineStr"/>
+      <c r="F856" t="inlineStr"/>
+      <c r="G856" t="inlineStr"/>
+      <c r="H856" t="inlineStr"/>
+      <c r="I856" t="n">
+        <v>0.05268459</v>
+      </c>
+      <c r="J856" t="inlineStr"/>
+      <c r="K856" t="n">
+        <v>1607.630644161081</v>
+      </c>
+      <c r="L856" t="inlineStr"/>
+      <c r="M856" t="inlineStr"/>
+      <c r="N856" t="inlineStr"/>
+      <c r="O856" t="n">
+        <v>0.009672861</v>
+      </c>
+      <c r="P856" t="inlineStr"/>
+      <c r="Q856" t="n">
+        <v>1.1448e-06</v>
+      </c>
+      <c r="R856" t="inlineStr"/>
+      <c r="S856" t="inlineStr"/>
+      <c r="T856" t="inlineStr"/>
+      <c r="U856" t="inlineStr"/>
+      <c r="V856" t="inlineStr"/>
+      <c r="W856" t="inlineStr"/>
+      <c r="X856" t="inlineStr"/>
+      <c r="Y856" t="inlineStr"/>
+      <c r="Z856" t="inlineStr"/>
+      <c r="AA856" t="n">
+        <v>0.8384278614544</v>
+      </c>
+      <c r="AB856" t="n">
+        <v>216.2290624925</v>
+      </c>
+      <c r="AC856" t="n">
+        <v>8.4031278382216</v>
+      </c>
+      <c r="AD856" t="n">
+        <v>0.121795245</v>
+      </c>
+      <c r="AE856" t="n">
+        <v>1834.056315054557</v>
+      </c>
+      <c r="AF856" t="inlineStr"/>
+      <c r="AG856" t="n">
+        <v>0.024665354</v>
+      </c>
+      <c r="AH856" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH856"/>
+  <dimension ref="A1:AH858"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66213,7 +66213,7 @@
         <v>0.11637301</v>
       </c>
       <c r="AE853" t="n">
-        <v>1816.980927733443</v>
+        <v>1816.980927733444</v>
       </c>
       <c r="AF853" t="inlineStr"/>
       <c r="AG853" t="n">
@@ -66407,6 +66407,130 @@
       </c>
       <c r="AH856" t="inlineStr"/>
     </row>
+    <row r="857">
+      <c r="A857" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B857" t="n">
+        <v>0.642253772</v>
+      </c>
+      <c r="C857" t="n">
+        <v>0.1000944505</v>
+      </c>
+      <c r="D857" t="inlineStr"/>
+      <c r="E857" t="inlineStr"/>
+      <c r="F857" t="inlineStr"/>
+      <c r="G857" t="inlineStr"/>
+      <c r="H857" t="inlineStr"/>
+      <c r="I857" t="n">
+        <v>0.052538367</v>
+      </c>
+      <c r="J857" t="inlineStr"/>
+      <c r="K857" t="n">
+        <v>1595.504622476083</v>
+      </c>
+      <c r="L857" t="inlineStr"/>
+      <c r="M857" t="inlineStr"/>
+      <c r="N857" t="inlineStr"/>
+      <c r="O857" t="n">
+        <v>0.009539397999999999</v>
+      </c>
+      <c r="P857" t="inlineStr"/>
+      <c r="Q857" t="n">
+        <v>1.1976e-06</v>
+      </c>
+      <c r="R857" t="inlineStr"/>
+      <c r="S857" t="inlineStr"/>
+      <c r="T857" t="inlineStr"/>
+      <c r="U857" t="inlineStr"/>
+      <c r="V857" t="inlineStr"/>
+      <c r="W857" t="inlineStr"/>
+      <c r="X857" t="inlineStr"/>
+      <c r="Y857" t="inlineStr"/>
+      <c r="Z857" t="inlineStr"/>
+      <c r="AA857" t="n">
+        <v>0.838360795944</v>
+      </c>
+      <c r="AB857" t="n">
+        <v>239.5352769825</v>
+      </c>
+      <c r="AC857" t="n">
+        <v>8.570817750735999</v>
+      </c>
+      <c r="AD857" t="n">
+        <v>0.157244815</v>
+      </c>
+      <c r="AE857" t="n">
+        <v>1845.435797151363</v>
+      </c>
+      <c r="AF857" t="inlineStr"/>
+      <c r="AG857" t="n">
+        <v>0.025047146</v>
+      </c>
+      <c r="AH857" t="inlineStr"/>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B858" t="n">
+        <v>0.62876212</v>
+      </c>
+      <c r="C858" t="n">
+        <v>0.09758920850000001</v>
+      </c>
+      <c r="D858" t="inlineStr"/>
+      <c r="E858" t="inlineStr"/>
+      <c r="F858" t="inlineStr"/>
+      <c r="G858" t="inlineStr"/>
+      <c r="H858" t="inlineStr"/>
+      <c r="I858" t="n">
+        <v>0.050952069</v>
+      </c>
+      <c r="J858" t="inlineStr"/>
+      <c r="K858" t="n">
+        <v>1595.971007925506</v>
+      </c>
+      <c r="L858" t="inlineStr"/>
+      <c r="M858" t="inlineStr"/>
+      <c r="N858" t="inlineStr"/>
+      <c r="O858" t="n">
+        <v>0.009285297999999999</v>
+      </c>
+      <c r="P858" t="inlineStr"/>
+      <c r="Q858" t="n">
+        <v>1.0416e-06</v>
+      </c>
+      <c r="R858" t="inlineStr"/>
+      <c r="S858" t="inlineStr"/>
+      <c r="T858" t="inlineStr"/>
+      <c r="U858" t="inlineStr"/>
+      <c r="V858" t="inlineStr"/>
+      <c r="W858" t="inlineStr"/>
+      <c r="X858" t="inlineStr"/>
+      <c r="Y858" t="inlineStr"/>
+      <c r="Z858" t="inlineStr"/>
+      <c r="AA858" t="n">
+        <v>0.8384110950768</v>
+      </c>
+      <c r="AB858" t="n">
+        <v>220.168782609</v>
+      </c>
+      <c r="AC858" t="n">
+        <v>8.049115800691199</v>
+      </c>
+      <c r="AD858" t="n">
+        <v>0.153781875</v>
+      </c>
+      <c r="AE858" t="n">
+        <v>1825.992282810374</v>
+      </c>
+      <c r="AF858" t="inlineStr"/>
+      <c r="AG858" t="n">
+        <v>0.024593768</v>
+      </c>
+      <c r="AH858" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH858"/>
+  <dimension ref="A1:AH859"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66213,7 +66213,7 @@
         <v>0.11637301</v>
       </c>
       <c r="AE853" t="n">
-        <v>1816.980927733444</v>
+        <v>1816.980927733443</v>
       </c>
       <c r="AF853" t="inlineStr"/>
       <c r="AG853" t="n">
@@ -66531,6 +66531,68 @@
       </c>
       <c r="AH858" t="inlineStr"/>
     </row>
+    <row r="859">
+      <c r="A859" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B859" t="n">
+        <v>0.628856288</v>
+      </c>
+      <c r="C859" t="n">
+        <v>0.09771061750000001</v>
+      </c>
+      <c r="D859" t="inlineStr"/>
+      <c r="E859" t="inlineStr"/>
+      <c r="F859" t="inlineStr"/>
+      <c r="G859" t="inlineStr"/>
+      <c r="H859" t="inlineStr"/>
+      <c r="I859" t="n">
+        <v>0.051860424</v>
+      </c>
+      <c r="J859" t="inlineStr"/>
+      <c r="K859" t="n">
+        <v>1587.109684386469</v>
+      </c>
+      <c r="L859" t="inlineStr"/>
+      <c r="M859" t="inlineStr"/>
+      <c r="N859" t="inlineStr"/>
+      <c r="O859" t="n">
+        <v>0.009397949000000001</v>
+      </c>
+      <c r="P859" t="inlineStr"/>
+      <c r="Q859" t="n">
+        <v>1.0632e-06</v>
+      </c>
+      <c r="R859" t="inlineStr"/>
+      <c r="S859" t="inlineStr"/>
+      <c r="T859" t="inlineStr"/>
+      <c r="U859" t="inlineStr"/>
+      <c r="V859" t="inlineStr"/>
+      <c r="W859" t="inlineStr"/>
+      <c r="X859" t="inlineStr"/>
+      <c r="Y859" t="inlineStr"/>
+      <c r="Z859" t="inlineStr"/>
+      <c r="AA859" t="n">
+        <v>0.8385200765312</v>
+      </c>
+      <c r="AB859" t="n">
+        <v>227.275267683</v>
+      </c>
+      <c r="AC859" t="n">
+        <v>8.8316687257584</v>
+      </c>
+      <c r="AD859" t="n">
+        <v>0.154419785</v>
+      </c>
+      <c r="AE859" t="n">
+        <v>1825.026001513459</v>
+      </c>
+      <c r="AF859" t="inlineStr"/>
+      <c r="AG859" t="n">
+        <v>0.028614515</v>
+      </c>
+      <c r="AH859" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH859"/>
+  <dimension ref="A1:AH860"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66213,7 +66213,7 @@
         <v>0.11637301</v>
       </c>
       <c r="AE853" t="n">
-        <v>1816.980927733443</v>
+        <v>1816.980927733444</v>
       </c>
       <c r="AF853" t="inlineStr"/>
       <c r="AG853" t="n">
@@ -66593,6 +66593,68 @@
       </c>
       <c r="AH859" t="inlineStr"/>
     </row>
+    <row r="860">
+      <c r="A860" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B860" t="n">
+        <v>0.6265449255000001</v>
+      </c>
+      <c r="C860" t="n">
+        <v>0.09784002350000001</v>
+      </c>
+      <c r="D860" t="inlineStr"/>
+      <c r="E860" t="inlineStr"/>
+      <c r="F860" t="inlineStr"/>
+      <c r="G860" t="inlineStr"/>
+      <c r="H860" t="inlineStr"/>
+      <c r="I860" t="n">
+        <v>0.054124665</v>
+      </c>
+      <c r="J860" t="inlineStr"/>
+      <c r="K860" t="n">
+        <v>1577.315589948586</v>
+      </c>
+      <c r="L860" t="inlineStr"/>
+      <c r="M860" t="inlineStr"/>
+      <c r="N860" t="inlineStr"/>
+      <c r="O860" t="n">
+        <v>0.009403273</v>
+      </c>
+      <c r="P860" t="inlineStr"/>
+      <c r="Q860" t="n">
+        <v>1.0776e-06</v>
+      </c>
+      <c r="R860" t="inlineStr"/>
+      <c r="S860" t="inlineStr"/>
+      <c r="T860" t="inlineStr"/>
+      <c r="U860" t="inlineStr"/>
+      <c r="V860" t="inlineStr"/>
+      <c r="W860" t="inlineStr"/>
+      <c r="X860" t="inlineStr"/>
+      <c r="Y860" t="inlineStr"/>
+      <c r="Z860" t="inlineStr"/>
+      <c r="AA860" t="n">
+        <v>0.8383943286991999</v>
+      </c>
+      <c r="AB860" t="n">
+        <v>228.6081010085</v>
+      </c>
+      <c r="AC860" t="n">
+        <v>8.8316687257584</v>
+      </c>
+      <c r="AD860" t="n">
+        <v>0.156424645</v>
+      </c>
+      <c r="AE860" t="n">
+        <v>1816.566961664143</v>
+      </c>
+      <c r="AF860" t="inlineStr"/>
+      <c r="AG860" t="n">
+        <v>0.028869043</v>
+      </c>
+      <c r="AH860" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH864"/>
+  <dimension ref="A1:AH865"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66903,6 +66903,68 @@
       </c>
       <c r="AH864" t="inlineStr"/>
     </row>
+    <row r="865">
+      <c r="A865" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B865" t="n">
+        <v>0.62299582</v>
+      </c>
+      <c r="C865" t="n">
+        <v>0.09763646350000002</v>
+      </c>
+      <c r="D865" t="inlineStr"/>
+      <c r="E865" t="inlineStr"/>
+      <c r="F865" t="inlineStr"/>
+      <c r="G865" t="inlineStr"/>
+      <c r="H865" t="inlineStr"/>
+      <c r="I865" t="n">
+        <v>0.052338972</v>
+      </c>
+      <c r="J865" t="inlineStr"/>
+      <c r="K865" t="n">
+        <v>1573.584506353202</v>
+      </c>
+      <c r="L865" t="inlineStr"/>
+      <c r="M865" t="inlineStr"/>
+      <c r="N865" t="inlineStr"/>
+      <c r="O865" t="n">
+        <v>0.009308166999999999</v>
+      </c>
+      <c r="P865" t="inlineStr"/>
+      <c r="Q865" t="n">
+        <v>1.0272e-06</v>
+      </c>
+      <c r="R865" t="inlineStr"/>
+      <c r="S865" t="inlineStr"/>
+      <c r="T865" t="inlineStr"/>
+      <c r="U865" t="inlineStr"/>
+      <c r="V865" t="inlineStr"/>
+      <c r="W865" t="inlineStr"/>
+      <c r="X865" t="inlineStr"/>
+      <c r="Y865" t="inlineStr"/>
+      <c r="Z865" t="inlineStr"/>
+      <c r="AA865" t="n">
+        <v>0.8388386377056001</v>
+      </c>
+      <c r="AB865" t="n">
+        <v>211.3738460565</v>
+      </c>
+      <c r="AC865" t="n">
+        <v>8.2727023507104</v>
+      </c>
+      <c r="AD865" t="n">
+        <v>0.13952003</v>
+      </c>
+      <c r="AE865" t="n">
+        <v>1795.018439202817</v>
+      </c>
+      <c r="AF865" t="inlineStr"/>
+      <c r="AG865" t="n">
+        <v>0.026745325</v>
+      </c>
+      <c r="AH865" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Positions.xlsx
+++ b/Positions.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH865"/>
+  <dimension ref="A1:AH867"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66213,7 +66213,7 @@
         <v>0.11637301</v>
       </c>
       <c r="AE853" t="n">
-        <v>1816.980927733444</v>
+        <v>1816.980927733443</v>
       </c>
       <c r="AF853" t="inlineStr"/>
       <c r="AG853" t="n">
@@ -66965,6 +66965,130 @@
       </c>
       <c r="AH865" t="inlineStr"/>
     </row>
+    <row r="866">
+      <c r="A866" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B866" t="n">
+        <v>0.6323563725</v>
+      </c>
+      <c r="C866" t="n">
+        <v>0.09837836700000001</v>
+      </c>
+      <c r="D866" t="inlineStr"/>
+      <c r="E866" t="inlineStr"/>
+      <c r="F866" t="inlineStr"/>
+      <c r="G866" t="inlineStr"/>
+      <c r="H866" t="inlineStr"/>
+      <c r="I866" t="n">
+        <v>0.05246747099999999</v>
+      </c>
+      <c r="J866" t="inlineStr"/>
+      <c r="K866" t="n">
+        <v>1561.458484668204</v>
+      </c>
+      <c r="L866" t="inlineStr"/>
+      <c r="M866" t="inlineStr"/>
+      <c r="N866" t="inlineStr"/>
+      <c r="O866" t="n">
+        <v>0.009338174999999999</v>
+      </c>
+      <c r="P866" t="inlineStr"/>
+      <c r="Q866" t="n">
+        <v>1.0632e-06</v>
+      </c>
+      <c r="R866" t="inlineStr"/>
+      <c r="S866" t="inlineStr"/>
+      <c r="T866" t="inlineStr"/>
+      <c r="U866" t="inlineStr"/>
+      <c r="V866" t="inlineStr"/>
+      <c r="W866" t="inlineStr"/>
+      <c r="X866" t="inlineStr"/>
+      <c r="Y866" t="inlineStr"/>
+      <c r="Z866" t="inlineStr"/>
+      <c r="AA866" t="n">
+        <v>0.8385787588528</v>
+      </c>
+      <c r="AB866" t="n">
+        <v>196.260074554</v>
+      </c>
+      <c r="AC866" t="n">
+        <v>8.2540701382088</v>
+      </c>
+      <c r="AD866" t="n">
+        <v>0.140932545</v>
+      </c>
+      <c r="AE866" t="n">
+        <v>1767.771773436965</v>
+      </c>
+      <c r="AF866" t="inlineStr"/>
+      <c r="AG866" t="n">
+        <v>0.027091324</v>
+      </c>
+      <c r="AH866" t="inlineStr"/>
+    </row>
+    <row r="867">
+      <c r="A867" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B867" t="n">
+        <v>0.6296591745</v>
+      </c>
+      <c r="C867" t="n">
+        <v>0.09700324650000001</v>
+      </c>
+      <c r="D867" t="inlineStr"/>
+      <c r="E867" t="inlineStr"/>
+      <c r="F867" t="inlineStr"/>
+      <c r="G867" t="inlineStr"/>
+      <c r="H867" t="inlineStr"/>
+      <c r="I867" t="n">
+        <v>0.052573815</v>
+      </c>
+      <c r="J867" t="inlineStr"/>
+      <c r="K867" t="n">
+        <v>1560.992099218781</v>
+      </c>
+      <c r="L867" t="inlineStr"/>
+      <c r="M867" t="inlineStr"/>
+      <c r="N867" t="inlineStr"/>
+      <c r="O867" t="n">
+        <v>0.009295824999999999</v>
+      </c>
+      <c r="P867" t="inlineStr"/>
+      <c r="Q867" t="n">
+        <v>1.02e-06</v>
+      </c>
+      <c r="R867" t="inlineStr"/>
+      <c r="S867" t="inlineStr"/>
+      <c r="T867" t="inlineStr"/>
+      <c r="U867" t="inlineStr"/>
+      <c r="V867" t="inlineStr"/>
+      <c r="W867" t="inlineStr"/>
+      <c r="X867" t="inlineStr"/>
+      <c r="Y867" t="inlineStr"/>
+      <c r="Z867" t="inlineStr"/>
+      <c r="AA867" t="n">
+        <v>0.8384781605871999</v>
+      </c>
+      <c r="AB867" t="n">
+        <v>191.252030482</v>
+      </c>
+      <c r="AC867" t="n">
+        <v>8.3285989882152</v>
+      </c>
+      <c r="AD867" t="n">
+        <v>0.14198054</v>
+      </c>
+      <c r="AE867" t="n">
+        <v>1762.369515723583</v>
+      </c>
+      <c r="AF867" t="inlineStr"/>
+      <c r="AG867" t="n">
+        <v>0.027795253</v>
+      </c>
+      <c r="AH867" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
